--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.72601899523109</v>
+        <v>4.017978086725053</v>
       </c>
       <c r="D2" t="n">
-        <v>24.6309464907929</v>
+        <v>4.002528804753846</v>
       </c>
       <c r="E2" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F2" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.57649409644948</v>
+        <v>7.081180290673041</v>
       </c>
       <c r="D3" t="n">
-        <v>43.81469022582387</v>
+        <v>7.11988716169638</v>
       </c>
       <c r="E3" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F3" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.00502762120569</v>
+        <v>7.963316988445925</v>
       </c>
       <c r="D4" t="n">
-        <v>48.89566150022721</v>
+        <v>7.945544993786921</v>
       </c>
       <c r="E4" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F4" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.61210506356014</v>
+        <v>6.436967072828522</v>
       </c>
       <c r="D5" t="n">
-        <v>39.54700247496699</v>
+        <v>6.426387902182135</v>
       </c>
       <c r="E5" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F5" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>66.57709785416928</v>
+        <v>10.81877840130251</v>
       </c>
       <c r="D6" t="n">
-        <v>66.26475472815915</v>
+        <v>10.76802264332586</v>
       </c>
       <c r="E6" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F6" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.51548525463806</v>
+        <v>6.908766353878685</v>
       </c>
       <c r="D7" t="n">
-        <v>42.25479082593866</v>
+        <v>6.866403509215033</v>
       </c>
       <c r="E7" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F7" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.74319027768674</v>
+        <v>5.970768420124095</v>
       </c>
       <c r="D8" t="n">
-        <v>36.73671944740898</v>
+        <v>5.969716910203959</v>
       </c>
       <c r="E8" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F8" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.72624605092623</v>
+        <v>3.205514983275513</v>
       </c>
       <c r="D9" t="n">
-        <v>20.11803757560606</v>
+        <v>3.269181106035985</v>
       </c>
       <c r="E9" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F9" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>59.08926125879064</v>
+        <v>9.602004954553479</v>
       </c>
       <c r="D10" t="n">
-        <v>58.67266948079407</v>
+        <v>9.534308790629037</v>
       </c>
       <c r="E10" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F10" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.22624408399183</v>
+        <v>3.936764663648673</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52936022413689</v>
+        <v>3.986021036422245</v>
       </c>
       <c r="E11" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F11" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.25132882269568</v>
+        <v>5.890840933688048</v>
       </c>
       <c r="D12" t="n">
-        <v>36.50198705629606</v>
+        <v>5.93157289664811</v>
       </c>
       <c r="E12" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F12" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.57745881783978</v>
+        <v>5.456337057898964</v>
       </c>
       <c r="D13" t="n">
-        <v>33.21455843921942</v>
+        <v>5.397365746373155</v>
       </c>
       <c r="E13" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F13" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>48.37957599437586</v>
+        <v>7.861681099086078</v>
       </c>
       <c r="D14" t="n">
-        <v>48.00990430578963</v>
+        <v>7.801609449690814</v>
       </c>
       <c r="E14" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F14" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>62.38978105859145</v>
+        <v>10.13833942202111</v>
       </c>
       <c r="D15" t="n">
-        <v>62.02810514830052</v>
+        <v>10.07956708659883</v>
       </c>
       <c r="E15" t="n">
-        <v>13.76303469699616</v>
+        <v>2.236493138261876</v>
       </c>
       <c r="F15" t="n">
-        <v>13.57838353758731</v>
+        <v>2.206487324857938</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
